--- a/site/User-Integration-Setup-Guide/headings.xlsx
+++ b/site/User-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>h_01G2KVKHHG6FK1QFNFMY9RE5XF</t>
+          <t>h_01KWER92B632N5KRN28G01J7CT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01G2KVKHHG6FK1QFNFMY9RE5XF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWER92B632N5KRN28G01J7CT</t>
         </is>
       </c>
     </row>
@@ -529,29 +529,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Create your own User Integration</t>
+          <t>Configuring User Integration</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>h_01HTHEEZS0CS7456JNRYRSF4A1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01HTHEEZS0CS7456JNRYRSF4A1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Create User Integration using a Template</t>
+          <t>Connections</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -561,63 +561,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>h_01HXY3V2PKJ1N45Z2DAJNE54H9</t>
+          <t>h_01KWGJQG4ZFDPV2JNMC0B73ASK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01HXY3V2PKJ1N45Z2DAJNE54H9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGJQG4ZFDPV2JNMC0B73ASK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Configuring User Integration</t>
+          <t>Source Application</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>h_01HTHEEZS0CS7456JNRYRSF4A1</t>
+          <t>h_01GYETCNZJJ82ZSS3JSKP4KH0Z</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01HTHEEZS0CS7456JNRYRSF4A1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETCNZJJ82ZSS3JSKP4KH0Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Basic Details</t>
+          <t>Target Application</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01H0PWCXWT6MJE5NCTTP63J2YS</t>
+          <t>h_01GYETDCC2FX7A96FZVS1MTD7Z</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWCXWT6MJE5NCTTP63J2YS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETDCC2FX7A96FZVS1MTD7Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Source Application</t>
+          <t>Match Expression</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -627,41 +627,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01GYETCNZJJ82ZSS3JSKP4KH0Z</t>
+          <t>h_01GYETEJHRGTX46BYBRFSKNFHG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETCNZJJ82ZSS3JSKP4KH0Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETEJHRGTX46BYBRFSKNFHG</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Target Application</t>
+          <t>Onboarding</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01GYETDCC2FX7A96FZVS1MTD7Z</t>
+          <t>h_01KWGNMZCTMMGESP0K07W6QR20</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETDCC2FX7A96FZVS1MTD7Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGNMZCTMMGESP0K07W6QR20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Report Only</t>
+          <t>Enable Onboarding</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01GYETDNX1PS5WSKG76W4CT719</t>
+          <t>h_01KWGNYCYYVH2G4D3EEC60TJCX</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETDNX1PS5WSKG76W4CT719</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGNYCYYVH2G4D3EEC60TJCX</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Update Limit</t>
+          <t>Create Condition</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,19 +693,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01GYETE7WXSJW507TZF27RYGC5</t>
+          <t>h_01GYETP0MHT03VXNH1DJ4HJ0QN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETE7WXSJW507TZF27RYGC5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETP0MHT03VXNH1DJ4HJ0QN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Admin Email List</t>
+          <t>Generate Password</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01GYETECR9587XW9EBDNH0M11D</t>
+          <t>h_01GYEVE0QG9NBNVYJMA6CPBJKA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETECR9587XW9EBDNH0M11D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVE0QG9NBNVYJMA6CPBJKA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Match Expression</t>
+          <t>Password Length</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01GYETEJHRGTX46BYBRFSKNFHG</t>
+          <t>h_01GYEVEP5SZ16HA43NK1MC9PGK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETEJHRGTX46BYBRFSKNFHG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVEP5SZ16HA43NK1MC9PGK</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Incremental Mode</t>
+          <t>Special Character Set for Password</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01GYETGEYHNKZC9G69SS47FFHV</t>
+          <t>h_01GYEVEYE5ENH9R0A53SAXSV2C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETGEYHNKZC9G69SS47FFHV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVEYE5ENH9R0A53SAXSV2C</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Import Limit</t>
+          <t>Enable Uniqueness Validation</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01GYETGYF8R1NB4RWM1WRRDWZ7</t>
+          <t>h_01KY4P1GSXZZHM1T73Z6NVASYG</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETGYF8R1NB4RWM1WRRDWZ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KY4P1GSXZZHM1T73Z6NVASYG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Source SCIM Filter</t>
+          <t>Validation Target Application</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01GYETHB98MMAZ5Q91SHB5ES0M</t>
+          <t>h_01KY4P327Z2P3AKKAY02DG9CN3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETHB98MMAZ5Q91SHB5ES0M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KY4P327Z2P3AKKAY02DG9CN3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Create Condition</t>
+          <t>Validation Attribute Name</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01GYETP0MHT03VXNH1DJ4HJ0QN</t>
+          <t>h_01KY4P3F75EMK23KEZCE467G0Q</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETP0MHT03VXNH1DJ4HJ0QN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KY4P3F75EMK23KEZCE467G0Q</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Update Condition</t>
+          <t>Send email on create</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01GYETP5N1ENJCFYKX52KXBAYE</t>
+          <t>h_01KWGP86F476QQ46FZ4JS8F9G8</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETP5N1ENJCFYKX52KXBAYE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGP86F476QQ46FZ4JS8F9G8</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Map Manager</t>
+          <t>Creation Distribution List</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01GYETPGFMDGR5BSJ91HPAZBJ6</t>
+          <t>h_01JKB0SDDCND2G096S1PA018EN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETPGFMDGR5BSJ91HPAZBJ6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01JKB0SDDCND2G096S1PA018EN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>New User Integration Hook</t>
+          <t>Notify Additional Recipients</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,19 +891,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01GYETPXFB90S2QM74D1EBPHZS</t>
+          <t>h_01KWGPC610CR7ERYRC6J2CPHBP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETPXFB90S2QM74D1EBPHZS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGPC610CR7ERYRC6J2CPHBP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Update User Integration Hook</t>
+          <t>Creation Email Subject</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -913,19 +913,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01HTHTZEWT4VB5211TY0FTZ059</t>
+          <t>h_01H259NX8ZQ1SG3CV99H73XA5M</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01HTHTZEWT4VB5211TY0FTZ059</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H259NX8ZQ1SG3CV99H73XA5M</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deprovision User Integration Hook</t>
+          <t>Creation Email Body</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01HTHTZEWTWTG692ZC61NN5D7T</t>
+          <t>h_01GYETVVWJR5NKPP04M0JA58SY</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01HTHTZEWTWTG692ZC61NN5D7T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETVVWJR5NKPP04M0JA58SY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fire Hooks on Error</t>
+          <t>Send Email To</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,63 +957,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01GYETRSSQ79QVM7DTMMS309H7</t>
+          <t>h_01GYETZD1PRWNQJ7DC4VV9PQAC</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETRSSQ79QVM7DTMMS309H7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETZD1PRWNQJ7DC4VV9PQAC</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Creation Email Details</t>
+          <t>New User Integration Hook</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01H0PWE7Q4GMR48G4DSVR28SDZ</t>
+          <t>h_01GYETPXFB90S2QM74D1EBPHZS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWE7Q4GMR48G4DSVR28SDZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETPXFB90S2QM74D1EBPHZS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Creation Distribution List</t>
+          <t>Profile Update</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01JKB0SDDCND2G096S1PA018EN</t>
+          <t>h_01KWGR1YXAMSN5QNNN6M6GVPQE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01JKB0SDDCND2G096S1PA018EN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGR1YXAMSN5QNNN6M6GVPQE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Creation Email Subject</t>
+          <t>Enable Profile Update</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01H259NX8ZQ1SG3CV99H73XA5M</t>
+          <t>h_01KWGR9TJZ64TWHETKQQ2FD030</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H259NX8ZQ1SG3CV99H73XA5M</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGR9TJZ64TWHETKQQ2FD030</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Creation Email Body</t>
+          <t>Update Condition</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,19 +1045,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01GYETVVWJR5NKPP04M0JA58SY</t>
+          <t>h_01GYETP5N1ENJCFYKX52KXBAYE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETVVWJR5NKPP04M0JA58SY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETP5N1ENJCFYKX52KXBAYE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Send as HTML</t>
+          <t>Update Deactivated Users</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01GYETXTZFN7PVT2VZ7KY9J9FS</t>
+          <t>h_01KWGRESFFZ6RNY2D5S8TE0ZPA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETXTZFN7PVT2VZ7KY9J9FS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGRESFFZ6RNY2D5S8TE0ZPA</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Send to Manager's Home Email</t>
+          <t>Update User Integration Hook</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1089,41 +1089,41 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01GYETY3WFJWKWZTJGX1E62W96</t>
+          <t>h_01KWGRH3XW5SEAS6VBMD21DJJ6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETY3WFJWKWZTJGX1E62W96</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGRH3XW5SEAS6VBMD21DJJ6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Send to Manager's Work Email</t>
+          <t>Offboarding</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01GYETYBJD0YAK1J8VVSN4YC8P</t>
+          <t>h_01KWGRRKWHZ077EJAWMJRS68B9</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETYBJD0YAK1J8VVSN4YC8P</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGRRKWHZ077EJAWMJRS68B9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Send to User's Home Email</t>
+          <t>Enable Offboarding</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1133,19 +1133,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01GYETYQ34EX0EZN44RXNSNK9Z</t>
+          <t>h_01KWGRYQA49XAK04C083XJ909Z</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETYQ34EX0EZN44RXNSNK9Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGRYQA49XAK04C083XJ909Z</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Send to User's Work Email</t>
+          <t>Delete Condition</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1155,19 +1155,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>h_01GYETZ4SBB3A7NNKH831Q8KVR</t>
+          <t>h_01KWGS09682ACBX6XGDSGM2EZX</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETZ4SBB3A7NNKH831Q8KVR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGS09682ACBX6XGDSGM2EZX</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Send Email To</t>
+          <t>Termination Delay</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1177,41 +1177,41 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>h_01GYETZD1PRWNQJ7DC4VV9PQAC</t>
+          <t>h_01KWGS2GBWHC4JBXJQHFRB8QN0</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETZD1PRWNQJ7DC4VV9PQAC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGS2GBWHC4JBXJQHFRB8QN0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deactivation Email Details</t>
+          <t>Deactivate Users Missing in the Source Application</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>h_01H0PWFZA455682M3PPYQ4RS9Z</t>
+          <t>h_01KWGS5GHRV763K3V2B2CN566X</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWFZA455682M3PPYQ4RS9Z</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGS5GHRV763K3V2B2CN566X</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deactivation Distribution List</t>
+          <t>Send Email on Deactivation</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1221,19 +1221,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>h_01GYEV4RQJ7X7X7M5KTXGE2WCV</t>
+          <t>h_01KWGS84MNF8WWY5G7123CBRYX</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEV4RQJ7X7X7M5KTXGE2WCV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGS84MNF8WWY5G7123CBRYX</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Deactivation Email Subject</t>
+          <t>Deactivation Distribution List</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01GYEV590SHHHN8B35CS5B80H2</t>
+          <t>h_01KWGSAW6MAKXZDQPWWYS78H52</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEV590SHHHN8B35CS5B80H2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGSAW6MAKXZDQPWWYS78H52</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deactivation Email Body</t>
+          <t>Notify Additional Recipients</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1265,19 +1265,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>h_01GYEV5F94P9X349C2H9K9EP21</t>
+          <t>h_01KWGSCKZDSK1V74ZACJM4B8PW</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEV5F94P9X349C2H9K9EP21</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGSCKZDSK1V74ZACJM4B8PW</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Send as HTML</t>
+          <t>Deactivation Email Subject</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1287,19 +1287,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>h_01GYEV6GTTV3FYF8J4Q38APZFQ</t>
+          <t>h_01GYEV590SHHHN8B35CS5B80H2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEV6GTTV3FYF8J4Q38APZFQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEV590SHHHN8B35CS5B80H2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Send to Manager's Home Email</t>
+          <t>Deactivation Email Body</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1309,19 +1309,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>h_01GYEV5XQHNY0CFDEGGMDE1VA1</t>
+          <t>h_01GYEV5F94P9X349C2H9K9EP21</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEV5XQHNY0CFDEGGMDE1VA1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEV5F94P9X349C2H9K9EP21</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Send to Manager's Work Email</t>
+          <t>Send Email To</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1331,19 +1331,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>h_01GYEV6Q4V8JVPXXQQED1J3QG7</t>
+          <t>h_01GYEV79ZHZZZFYBGQP7BJDRPX</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEV6Q4V8JVPXXQQED1J3QG7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEV79ZHZZZFYBGQP7BJDRPX</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Send Email To</t>
+          <t>Deprovision User Integration Hook</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1353,19 +1353,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>h_01GYEV79ZHZZZFYBGQP7BJDRPX</t>
+          <t>h_01HTHTZEWTWTG692ZC61NN5D7T</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEV79ZHZZZFYBGQP7BJDRPX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01HTHTZEWTWTG692ZC61NN5D7T</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Advanced Details</t>
+          <t>Additional Settings</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1375,19 +1375,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01H0PWEQMF76RHVC3PKQMW1QD5</t>
+          <t>h_01H0PWE7Q4GMR48G4DSVR28SDZ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWEQMF76RHVC3PKQMW1QD5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWE7Q4GMR48G4DSVR28SDZ</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Termination Delay</t>
+          <t>Source Filter Condition</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1397,19 +1397,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01GYEVAKNVE9NSGAKPW41RHWWM</t>
+          <t>h_01KWGT47CFB0MZ1YH6Y033SKVV</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVAKNVE9NSGAKPW41RHWWM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGT47CFB0MZ1YH6Y033SKVV</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Delete Condition</t>
+          <t>Map Manager</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,19 +1419,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01H19PR6Y48E2VN9G2HA4HXATZ</t>
+          <t>h_01KWGT55CNZ6JAP8K9EHWYM7MH</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H19PR6Y48E2VN9G2HA4HXATZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGT55CNZ6JAP8K9EHWYM7MH</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Allow Creation of Inactive Users</t>
+          <t>Phone Number Formatting</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KE69BCXSJDF0XCBNEVWGVM9X</t>
+          <t>h_01KWGT7AMCV2ZDS7QX1NSAZ3AK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KE69BCXSJDF0XCBNEVWGVM9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGT7AMCV2ZDS7QX1NSAZ3AK</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Source Caching</t>
+          <t>Timezone Offset</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,19 +1463,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01H4FXGA8H8AXM7J6EKD9K82CD</t>
+          <t>h_01KWGT9A8C5NW45EEZGRDWAWBR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H4FXGA8H8AXM7J6EKD9K82CD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGT9A8C5NW45EEZGRDWAWBR</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Target Caching</t>
+          <t>Fire Hooks on Error</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01H4FXGQ3QSVGX39ZH5T0MVWRC</t>
+          <t>h_01KWGTB2BTMW47KWPCKPZTY6S6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H4FXGQ3QSVGX39ZH5T0MVWRC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGTB2BTMW47KWPCKPZTY6S6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Deactivate Users Missing in the Source Application</t>
+          <t>Skip Create and Update Failures</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1507,19 +1507,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01GYEVBHHRZFZY0BG6P8MYP3G0</t>
+          <t>h_01GYEVG1HBZN86JG7D8WH8FM49</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVBHHRZFZY0BG6P8MYP3G0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVG1HBZN86JG7D8WH8FM49</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Incremental Mode Initial Timestamp</t>
+          <t>Destination Modification Safeguard Enabled</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1529,19 +1529,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01GYEVBZ54SZ63840YH2ZBM5DT</t>
+          <t>h_01GYEVGW0M92W3Q9D4419SF7ZF</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVBZ54SZ63840YH2ZBM5DT</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVGW0M92W3Q9D4419SF7ZF</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Incremental Mode Timestamp</t>
+          <t>Max Destination Modification Percentage</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,19 +1551,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01GYEVCGYPPY5410T1429GMF7F</t>
+          <t>h_01GYEVH51ZE4NF5D635MBEWFNW</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVCGYPPY5410T1429GMF7F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVH51ZE4NF5D635MBEWFNW</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Enable Incremental Cutoff</t>
+          <t>Incremental Tuning</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1573,41 +1573,41 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01GYEVCZCAZVKGRCK5VX2XTD2N</t>
+          <t>h_01GYEVNE9WVDNKEZT0HN1JCDWW</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVCZCAZVKGRCK5VX2XTD2N</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVNE9WVDNKEZT0HN1JCDWW</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Incremental Cutoff Limit</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>01JE3PARYFCR2D6NA1ZGRHZ9BG</t>
+          <t>h_01KWGTWAT6BSMZXAB98P9Q6FFT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#01JE3PARYFCR2D6NA1ZGRHZ9BG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGTWAT6BSMZXAB98P9Q6FFT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Enable Group Management</t>
+          <t>Incremental Mode</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1617,19 +1617,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>h_01JKB0SDDDQTSJHPQCA1Q90WQ0</t>
+          <t>h_01GYETGEYHNKZC9G69SS47FFHV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01JKB0SDDDQTSJHPQCA1Q90WQ0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETGEYHNKZC9G69SS47FFHV</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Group Management Restriction List</t>
+          <t>Incremental Mode Timestamp</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1639,19 +1639,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>h_01GYEVDBQFKKCJM5N4MWVE027F</t>
+          <t>h_01GYEVCGYPPY5410T1429GMF7F</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVDBQFKKCJM5N4MWVE027F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVCGYPPY5410T1429GMF7F</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Phone Number Formatting</t>
+          <t>Enable Incremental Cutoff</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1661,19 +1661,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01GYEVDNY3YNY3R6W19BN7NRQY</t>
+          <t>h_01GYEVCZCAZVKGRCK5VX2XTD2N</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVDNY3YNY3R6W19BN7NRQY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVCZCAZVKGRCK5VX2XTD2N</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Generate Password</t>
+          <t>Incremental Cutoff Limit</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1683,19 +1683,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01GYEVE0QG9NBNVYJMA6CPBJKA</t>
+          <t>01JE3PARYFCR2D6NA1ZGRHZ9BG</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVE0QG9NBNVYJMA6CPBJKA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#01JE3PARYFCR2D6NA1ZGRHZ9BG</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Password Length</t>
+          <t>Allow Creation of Inactive Users</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1705,19 +1705,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01GYEVEP5SZ16HA43NK1MC9PGK</t>
+          <t>h_01KWGVC2VWGYSCA3WZZRN3W7Y5</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVEP5SZ16HA43NK1MC9PGK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGVC2VWGYSCA3WZZRN3W7Y5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Special Character Set for Password</t>
+          <t>Report Only</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1727,19 +1727,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01GYEVEYE5ENH9R0A53SAXSV2C</t>
+          <t>h_01GYETDNX1PS5WSKG76W4CT719</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVEYE5ENH9R0A53SAXSV2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETDNX1PS5WSKG76W4CT719</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Report Mode</t>
+          <t>Import Limit</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1749,19 +1749,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01GYEVFBWZCHNAKY3VTCDBNBVH</t>
+          <t>h_01GYETGYF8R1NB4RWM1WRRDWZ7</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVFBWZCHNAKY3VTCDBNBVH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETGYF8R1NB4RWM1WRRDWZ7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Timezone Offset</t>
+          <t>Update Limit</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1771,19 +1771,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01GYEVFNFSXTW13A32ZP0YEMBB</t>
+          <t>h_01GYETE7WXSJW507TZF27RYGC5</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVFNFSXTW13A32ZP0YEMBB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYETE7WXSJW507TZF27RYGC5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Skip Create and Update Failures</t>
+          <t>Source Caching</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1793,19 +1793,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01GYEVG1HBZN86JG7D8WH8FM49</t>
+          <t>h_01H4FXGA8H8AXM7J6EKD9K82CD</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVG1HBZN86JG7D8WH8FM49</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H4FXGA8H8AXM7J6EKD9K82CD</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Update Deactivated Users</t>
+          <t>Target Caching</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1815,41 +1815,41 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>h_01GYEVGC8PYJCHK72VFRJ7S7SA</t>
+          <t>h_01H4FXGQ3QSVGX39ZH5T0MVWRC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVGC8PYJCHK72VFRJ7S7SA</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H4FXGQ3QSVGX39ZH5T0MVWRC</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Email From Address</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>h_01GYEVK9GV9MWXZX76FAY2NSCH</t>
+          <t>h_01KWGZ26RMX00SXBD89E4ENTWQ</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVK9GV9MWXZX76FAY2NSCH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGZ26RMX00SXBD89E4ENTWQ</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Destination Modification Safeguard Enabled</t>
+          <t>Report Mode</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1859,19 +1859,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>h_01GYEVGW0M92W3Q9D4419SF7ZF</t>
+          <t>h_01KWGZ9SSDKJDXMD2DHFJNMY0N</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVGW0M92W3Q9D4419SF7ZF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGZ9SSDKJDXMD2DHFJNMY0N</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Max Destination Modification Percentage</t>
+          <t>Email From Address</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1881,19 +1881,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h_01GYEVH51ZE4NF5D635MBEWFNW</t>
+          <t>h_01KWGZCADF0JGQD43XDJXQ9QR8</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVH51ZE4NF5D635MBEWFNW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGZCADF0JGQD43XDJXQ9QR8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Incremental Tuning</t>
+          <t>Send Reports</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1903,41 +1903,41 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>h_01GYEVNE9WVDNKEZT0HN1JCDWW</t>
+          <t>h_01KWGZEG1647WF3PR2TZ7PE26E</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GYEVNE9WVDNKEZT0HN1JCDWW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGZEG1647WF3PR2TZ7PE26E</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Admin Email Options</t>
+          <t>To</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>h_01H0PWK1BH6403K59XYNY78KD8</t>
+          <t>h_01KWGZF1NY3SE5RBGVHGD34YE8</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWK1BH6403K59XYNY78KD8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGZF1NY3SE5RBGVHGD34YE8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Admin Email Subject</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1947,19 +1947,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>h_01H18ZXG1MF6KMV82NXFJ4MHQJ</t>
+          <t>h_01KWGZG2RYD7330C8Q9Z1QKDJ0</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H18ZXG1MF6KMV82NXFJ4MHQJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGZG2RYD7330C8Q9Z1QKDJ0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Send Always</t>
+          <t>Send On</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>h_01H0PWKBH21GJGEMPVVA1HRRG8</t>
+          <t>h_01KWGZGQET1N1ACJJBBMRQT82W</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWKBH21GJGEMPVVA1HRRG8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGZGQET1N1ACJJBBMRQT82W</t>
         </is>
       </c>
     </row>
@@ -1991,19 +1991,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>h_01H190ERFH6M2EK0F999HNFQXJ</t>
+          <t>h_01KWGZHPWD5AY7S9Q8K96E0ZFC</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H190ERFH6M2EK0F999HNFQXJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGZHPWD5AY7S9Q8K96E0ZFC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Send on Report Only</t>
+          <t>Send Details</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2013,19 +2013,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>h_01H0PWKN1B22B7QACR36KGJH25</t>
+          <t>h_01H0PWNGBTBQWYHE2XFFR204FR</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWKN1B22B7QACR36KGJH25</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWNGBTBQWYHE2XFFR204FR</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Send on Update</t>
+          <t>Send CSV Report</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2035,19 +2035,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>h_01H0PWKZY3V5S9BB3Q0ATNMC07</t>
+          <t>01HA4R2VGTJABRTFVS6PQWM3EJ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWKZY3V5S9BB3Q0ATNMC07</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#01HA4R2VGTJABRTFVS6PQWM3EJ</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Send on Failure</t>
+          <t>Send XLSX Report</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2057,19 +2057,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>h_01H0PWMCKG8J0TDKW5EMGHSXPB</t>
+          <t>h_01KWGZR2TWG88H36WE5Y3368S2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWMCKG8J0TDKW5EMGHSXPB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWGZR2TWG88H36WE5Y3368S2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Send on Error</t>
+          <t>Dashboard Insights Level</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2079,41 +2079,41 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>h_01H0PWMT37FNYF6BYSJAM34DQQ</t>
+          <t>h_01KM274GVJ6BXEG2BQ609KGJ8J</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWMT37FNYF6BYSJAM34DQQ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KM274GVJ6BXEG2BQ609KGJ8J</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Send on Safeguard Trigger</t>
+          <t>Monitor Provisioning</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>h_01H18PBV832KK8GNB26M2PYG8A</t>
+          <t>h_01KWH04GZRVX5V11JNPEAQSNKA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H18PBV832KK8GNB26M2PYG8A</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWH04GZRVX5V11JNPEAQSNKA</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Send Details</t>
+          <t>Enable Monitoring</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2123,210 +2123,386 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>h_01H0PWNGBTBQWYHE2XFFR204FR</t>
+          <t>h_01KWH095BE00DK6PDC18567J7K</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0PWNGBTBQWYHE2XFFR204FR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWH095BE00DK6PDC18567J7K</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Send CSV Report</t>
+          <t>Mapping and Assignments</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>01HA4R2VGTJABRTFVS6PQWM3EJ</t>
+          <t>h_01EZA579V8NBAKB6Z4MSD9BNEX</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#01HA4R2VGTJABRTFVS6PQWM3EJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01EZA579V8NBAKB6Z4MSD9BNEX</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Integration Email Report</t>
+          <t>Group Management</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>01H80V60TEMX951022SDVMQR16</t>
+          <t>h_01KWHD2E95DP5R4SF1CRPBBQYY</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#01H80V60TEMX951022SDVMQR16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KWHD2E95DP5R4SF1CRPBBQYY</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Destination Modification Safeguard Scenarios</t>
+          <t>Set Up Group Rules</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>h_01GZE74XTR2GYT5CCHPC18MD54</t>
+          <t>h_01JVVCS2ZB17E6WN9ZMX0DSJQ7</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GZE74XTR2GYT5CCHPC18MD54</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01JVVCS2ZB17E6WN9ZMX0DSJQ7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mapping of Attributes</t>
+          <t>Using Condition Builder</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>h_01EZA579V8NBAKB6Z4MSD9BNEX</t>
+          <t>h_01KM0H9RTRKRPWDXNTDVVVD7FR</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01EZA579V8NBAKB6Z4MSD9BNEX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KM0H9RTRKRPWDXNTDVVVD7FR</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Adding and Using Tables</t>
+          <t>Using Expressions</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>h_01H0FK9NTH1QBANBJQ9Q4S0B17</t>
+          <t>h_01KM0HAHDDAJMYYBC477MCE3Z9</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0FK9NTH1QBANBJQ9Q4S0B17</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KM0HAHDDAJMYYBC477MCE3Z9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Setting Group Rules</t>
+          <t>Disabling or Enabling Group Rules</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>h_01F1QC3H37KV004GFERDM590W9</t>
+          <t>h_01KSF3CDA5TB8J88XZG0G0GZS7</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01F1QC3H37KV004GFERDM590W9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KSF3CDA5TB8J88XZG0G0GZS7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Scheduling Integration Run</t>
+          <t>Import Group Rules</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>h_01HTYZGYTMZCKJNBMK6QXPDH5K</t>
+          <t>h_01KS4TMFG3T0SHVPVNQTKK2PM4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01HTYZGYTMZCKJNBMK6QXPDH5K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KS4TMFG3T0SHVPVNQTKK2PM4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>User Actions on Integrations</t>
+          <t>Export Group Rules</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>h_01GMT3K6QJFHJSA0XYF3FJEW16</t>
+          <t>h_01KS4TMFG4YQGEPBCCEGVCAE7K</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GMT3K6QJFHJSA0XYF3FJEW16</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KS4TMFG4YQGEPBCCEGVCAE7K</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>Set Up Group Retention Policy</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>h_01JVVCWC8T23P8VMRGXP3X4CJV</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01JVVCWC8T23P8VMRGXP3X4CJV</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>On Deactivate/Deletion</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>h_01JVVDNXZWRT83NPP8MVZ9DXRJ</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01JVVDNXZWRT83NPP8MVZ9DXRJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>On Update</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>h_01JVVTGA4ZWZEXCZMPF6F19FCQ</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01JVVTGA4ZWZEXCZMPF6F19FCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Group Assignments Analysis</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>h_01KM2EHY8GF7C6W37NE9G031R2</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KM2EHY8GF7C6W37NE9G031R2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>h_01H02H9WB603XRNADRN1EK60SB</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H02H9WB603XRNADRN1EK60SB</t>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>h_01H0FK9NTH1QBANBJQ9Q4S0B17</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01H0FK9NTH1QBANBJQ9Q4S0B17</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>h_01HTYZGYTMZCKJNBMK6QXPDH5K</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01HTYZGYTMZCKJNBMK6QXPDH5K</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Appendix</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Destination Modification Safeguard Scenarios</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>h_01GZE74XTR2GYT5CCHPC18MD54</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01GZE74XTR2GYT5CCHPC18MD54</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Integration Execution Report in Excel Format</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>h_01KS2285RT7WYFNV6MSFDBDZPG</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01KS2285RT7WYFNV6MSFDBDZPG</t>
         </is>
       </c>
     </row>

--- a/site/User-Integration-Setup-Guide/headings.xlsx
+++ b/site/User-Integration-Setup-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2506,6 +2506,50 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Integration Logs</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>h_01M1B2BZ41065XG0H41AZSYK8Y</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01M1B2BZ41065XG0H41AZSYK8Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>h_01M1B2DKK08B01F03ZSC8FSVZB</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/User-Integration-Setup-Guide/#h_01M1B2DKK08B01F03ZSC8FSVZB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
